--- a/src/Golf.xlsx
+++ b/src/Golf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10312"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jgilson1/Documents/Github/Source/PersonalSite/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E4BD60-4CDD-A146-BACE-DF979CC7B3BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D4F8F0-D95B-8C45-A6FB-A1BE8AEAF742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" xr2:uid="{5A2DB70E-0041-3946-A9D9-B12F382827A1}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="20500" firstSheet="3" activeTab="17" xr2:uid="{5A2DB70E-0041-3946-A9D9-B12F382827A1}"/>
   </bookViews>
   <sheets>
     <sheet name="Anderson Glen" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="Stanley - Blue" sheetId="15" r:id="rId15"/>
     <sheet name="Portland West" sheetId="16" r:id="rId16"/>
     <sheet name="Keney Park" sheetId="17" r:id="rId17"/>
+    <sheet name="South Suburban" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8116" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8358" uniqueCount="516">
   <si>
     <t>Hole 1</t>
   </si>
@@ -1929,6 +1930,25 @@
   <si>
     <t>220, 114</t>
   </si>
+  <si>
+    <t>3/24/23
+1
+Mike
+Bob
+Rich</t>
+  </si>
+  <si>
+    <t>165, 5</t>
+  </si>
+  <si>
+    <t>21, 12</t>
+  </si>
+  <si>
+    <t>275, 65</t>
+  </si>
+  <si>
+    <t>275, 50</t>
+  </si>
 </sst>
 </file>
 
@@ -33067,6 +33087,1577 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998BC9EC-E479-054F-9095-3CA5188A4199}">
+  <dimension ref="A1:FY42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="64" max="64" width="10.83203125" style="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="B1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AF1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AM1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AR1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AS1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AT1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="AY1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="AZ1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="BA1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="BG1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="BH1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="BM1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="BN1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="BO1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="BT1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="BU1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="BV1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="CA1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="CB1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="CC1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="CH1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="CI1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="CJ1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="CO1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="CP1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="CQ1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="CV1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="CW1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="CX1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="DC1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="DD1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="DE1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="DJ1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="DK1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="DL1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="DQ1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="DR1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="DS1" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="B2">
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>338</v>
+      </c>
+      <c r="D2">
+        <v>17</v>
+      </c>
+      <c r="I2">
+        <v>5</v>
+      </c>
+      <c r="J2">
+        <v>490</v>
+      </c>
+      <c r="K2">
+        <v>15</v>
+      </c>
+      <c r="P2">
+        <v>4</v>
+      </c>
+      <c r="Q2">
+        <v>408</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="W2">
+        <v>3</v>
+      </c>
+      <c r="X2">
+        <v>194</v>
+      </c>
+      <c r="Y2">
+        <v>9</v>
+      </c>
+      <c r="AD2">
+        <v>4</v>
+      </c>
+      <c r="AE2">
+        <v>373</v>
+      </c>
+      <c r="AF2">
+        <v>11</v>
+      </c>
+      <c r="AK2">
+        <v>5</v>
+      </c>
+      <c r="AL2">
+        <v>613</v>
+      </c>
+      <c r="AM2">
+        <v>7</v>
+      </c>
+      <c r="AR2">
+        <v>4</v>
+      </c>
+      <c r="AS2">
+        <v>421</v>
+      </c>
+      <c r="AT2">
+        <v>3</v>
+      </c>
+      <c r="AY2">
+        <v>3</v>
+      </c>
+      <c r="AZ2">
+        <v>192</v>
+      </c>
+      <c r="BA2">
+        <v>13</v>
+      </c>
+      <c r="BF2">
+        <v>4</v>
+      </c>
+      <c r="BG2">
+        <v>435</v>
+      </c>
+      <c r="BH2">
+        <v>5</v>
+      </c>
+      <c r="BM2">
+        <v>4</v>
+      </c>
+      <c r="BN2">
+        <v>371</v>
+      </c>
+      <c r="BO2">
+        <v>16</v>
+      </c>
+      <c r="BT2">
+        <v>5</v>
+      </c>
+      <c r="BU2">
+        <v>555</v>
+      </c>
+      <c r="BV2">
+        <v>14</v>
+      </c>
+      <c r="CA2">
+        <v>4</v>
+      </c>
+      <c r="CB2">
+        <v>426</v>
+      </c>
+      <c r="CC2">
+        <v>2</v>
+      </c>
+      <c r="CH2">
+        <v>3</v>
+      </c>
+      <c r="CI2">
+        <v>194</v>
+      </c>
+      <c r="CJ2">
+        <v>12</v>
+      </c>
+      <c r="CO2">
+        <v>5</v>
+      </c>
+      <c r="CP2">
+        <v>598</v>
+      </c>
+      <c r="CQ2">
+        <v>8</v>
+      </c>
+      <c r="CV2">
+        <v>4</v>
+      </c>
+      <c r="CW2">
+        <v>379</v>
+      </c>
+      <c r="CX2">
+        <v>10</v>
+      </c>
+      <c r="DC2">
+        <v>3</v>
+      </c>
+      <c r="DD2">
+        <v>202</v>
+      </c>
+      <c r="DE2">
+        <v>6</v>
+      </c>
+      <c r="DJ2">
+        <v>4</v>
+      </c>
+      <c r="DK2">
+        <v>368</v>
+      </c>
+      <c r="DL2">
+        <v>18</v>
+      </c>
+      <c r="DQ2">
+        <v>4</v>
+      </c>
+      <c r="DR2">
+        <v>403</v>
+      </c>
+      <c r="DS2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J3" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" t="s">
+        <v>2</v>
+      </c>
+      <c r="S3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T3" t="s">
+        <v>7</v>
+      </c>
+      <c r="U3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V3" t="s">
+        <v>6</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="AE3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AI3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AK3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AM3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BC3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="BK3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="BL3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="BN3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BP3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BR3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BS3" t="s">
+        <v>6</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BW3" t="s">
+        <v>3</v>
+      </c>
+      <c r="BX3" t="s">
+        <v>7</v>
+      </c>
+      <c r="BY3" t="s">
+        <v>8</v>
+      </c>
+      <c r="BZ3" t="s">
+        <v>6</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>1</v>
+      </c>
+      <c r="CC3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CD3" t="s">
+        <v>3</v>
+      </c>
+      <c r="CE3" t="s">
+        <v>7</v>
+      </c>
+      <c r="CF3" t="s">
+        <v>8</v>
+      </c>
+      <c r="CG3" t="s">
+        <v>6</v>
+      </c>
+      <c r="CH3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="CI3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CJ3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CK3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CL3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CM3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="CN3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="CP3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CQ3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CR3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CS3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="CT3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="CU3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="CV3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="CW3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="CX3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="CY3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="CZ3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DA3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="DB3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="DC3" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="DD3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DE3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="DF3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="DG3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DH3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="DI3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="DJ3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="DK3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DL3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="DM3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="DN3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DO3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="DP3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="DQ3" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="DR3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="DS3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="DT3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="DU3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="DV3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="DW3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="DY3" s="1"/>
+      <c r="DZ3" s="1"/>
+      <c r="EA3" s="1"/>
+      <c r="EB3" s="1"/>
+      <c r="EC3" s="1"/>
+      <c r="ED3" s="1"/>
+      <c r="EE3" s="1"/>
+      <c r="EF3" s="1"/>
+      <c r="EH3" s="1"/>
+      <c r="EI3" s="1"/>
+      <c r="EJ3" s="1"/>
+      <c r="EK3" s="1"/>
+      <c r="EL3" s="1"/>
+      <c r="EM3" s="1"/>
+      <c r="EN3" s="1"/>
+      <c r="EO3" s="1"/>
+      <c r="EQ3" s="1"/>
+      <c r="ER3" s="1"/>
+      <c r="ES3" s="1"/>
+      <c r="ET3" s="1"/>
+      <c r="EU3" s="1"/>
+      <c r="EV3" s="1"/>
+      <c r="EW3" s="1"/>
+      <c r="EX3" s="1"/>
+      <c r="EZ3" s="1"/>
+      <c r="FA3" s="1"/>
+      <c r="FB3" s="1"/>
+      <c r="FC3" s="1"/>
+      <c r="FD3" s="1"/>
+      <c r="FE3" s="1"/>
+      <c r="FF3" s="1"/>
+      <c r="FG3" s="1"/>
+      <c r="FI3" s="1"/>
+      <c r="FJ3" s="1"/>
+      <c r="FK3" s="1"/>
+      <c r="FL3" s="1"/>
+      <c r="FM3" s="1"/>
+      <c r="FN3" s="1"/>
+      <c r="FO3" s="1"/>
+      <c r="FP3" s="1"/>
+      <c r="FQ3" s="1"/>
+      <c r="FR3" s="1"/>
+      <c r="FS3" s="1"/>
+      <c r="FT3" s="1"/>
+      <c r="FU3" s="1"/>
+      <c r="FV3" s="1"/>
+      <c r="FW3" s="1"/>
+      <c r="FX3" s="1"/>
+      <c r="FY3" s="1"/>
+    </row>
+    <row r="4" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4">
+        <v>45</v>
+      </c>
+      <c r="G4" t="s">
+        <v>113</v>
+      </c>
+      <c r="I4">
+        <v>4</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" t="s">
+        <v>512</v>
+      </c>
+      <c r="N4">
+        <v>18</v>
+      </c>
+      <c r="O4" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4">
+        <v>5</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4" t="s">
+        <v>27</v>
+      </c>
+      <c r="S4" t="s">
+        <v>5</v>
+      </c>
+      <c r="T4">
+        <v>170</v>
+      </c>
+      <c r="U4">
+        <v>15</v>
+      </c>
+      <c r="V4" t="s">
+        <v>68</v>
+      </c>
+      <c r="W4">
+        <v>3</v>
+      </c>
+      <c r="X4">
+        <v>2</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AA4">
+        <v>158</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>513</v>
+      </c>
+      <c r="AD4">
+        <v>4</v>
+      </c>
+      <c r="AE4">
+        <v>3</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AH4">
+        <v>373</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK4">
+        <v>5</v>
+      </c>
+      <c r="AL4">
+        <v>2</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>13</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>514</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AR4">
+        <v>6</v>
+      </c>
+      <c r="AS4">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AU4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AV4">
+        <v>80</v>
+      </c>
+      <c r="AW4" t="s">
+        <v>106</v>
+      </c>
+      <c r="AX4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AY4">
+        <v>4</v>
+      </c>
+      <c r="AZ4">
+        <v>3</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>26</v>
+      </c>
+      <c r="BB4" t="s">
+        <v>13</v>
+      </c>
+      <c r="BC4">
+        <v>165</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>122</v>
+      </c>
+      <c r="BE4" t="s">
+        <v>46</v>
+      </c>
+      <c r="BF4">
+        <v>5</v>
+      </c>
+      <c r="BG4">
+        <v>3</v>
+      </c>
+      <c r="BH4" t="s">
+        <v>18</v>
+      </c>
+      <c r="BI4" t="s">
+        <v>13</v>
+      </c>
+      <c r="BJ4">
+        <v>120</v>
+      </c>
+      <c r="BK4" t="s">
+        <v>113</v>
+      </c>
+      <c r="BL4" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="BM4">
+        <v>4</v>
+      </c>
+      <c r="BN4">
+        <v>2</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>18</v>
+      </c>
+      <c r="BP4" t="s">
+        <v>13</v>
+      </c>
+      <c r="BQ4">
+        <v>80</v>
+      </c>
+      <c r="BR4" t="s">
+        <v>103</v>
+      </c>
+      <c r="BT4">
+        <v>3</v>
+      </c>
+      <c r="BU4">
+        <v>1</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>18</v>
+      </c>
+      <c r="BW4" t="s">
+        <v>30</v>
+      </c>
+      <c r="BX4">
+        <v>230</v>
+      </c>
+      <c r="BY4">
+        <v>24</v>
+      </c>
+      <c r="CA4">
+        <v>5</v>
+      </c>
+      <c r="CB4">
+        <v>3</v>
+      </c>
+      <c r="CC4" t="s">
+        <v>18</v>
+      </c>
+      <c r="CD4" t="s">
+        <v>13</v>
+      </c>
+      <c r="CE4">
+        <v>135</v>
+      </c>
+      <c r="CF4" t="s">
+        <v>106</v>
+      </c>
+      <c r="CG4" t="s">
+        <v>46</v>
+      </c>
+      <c r="CH4">
+        <v>5</v>
+      </c>
+      <c r="CI4">
+        <v>3</v>
+      </c>
+      <c r="CJ4" t="s">
+        <v>26</v>
+      </c>
+      <c r="CK4" t="s">
+        <v>5</v>
+      </c>
+      <c r="CL4">
+        <v>175</v>
+      </c>
+      <c r="CM4" t="s">
+        <v>101</v>
+      </c>
+      <c r="CN4" t="s">
+        <v>46</v>
+      </c>
+      <c r="CO4">
+        <v>5</v>
+      </c>
+      <c r="CP4">
+        <v>2</v>
+      </c>
+      <c r="CQ4" t="s">
+        <v>18</v>
+      </c>
+      <c r="CR4" t="s">
+        <v>13</v>
+      </c>
+      <c r="CS4" t="s">
+        <v>515</v>
+      </c>
+      <c r="CT4" t="s">
+        <v>104</v>
+      </c>
+      <c r="CV4">
+        <v>4</v>
+      </c>
+      <c r="CW4">
+        <v>2</v>
+      </c>
+      <c r="CX4" t="s">
+        <v>18</v>
+      </c>
+      <c r="CY4" t="s">
+        <v>13</v>
+      </c>
+      <c r="CZ4">
+        <v>95</v>
+      </c>
+      <c r="DA4" t="s">
+        <v>104</v>
+      </c>
+      <c r="DC4">
+        <v>2</v>
+      </c>
+      <c r="DD4">
+        <v>1</v>
+      </c>
+      <c r="DE4" t="s">
+        <v>26</v>
+      </c>
+      <c r="DF4" t="s">
+        <v>13</v>
+      </c>
+      <c r="DG4">
+        <v>195</v>
+      </c>
+      <c r="DH4">
+        <v>12</v>
+      </c>
+      <c r="DJ4">
+        <v>5</v>
+      </c>
+      <c r="DK4">
+        <v>2</v>
+      </c>
+      <c r="DL4" t="s">
+        <v>4</v>
+      </c>
+      <c r="DM4" t="s">
+        <v>5</v>
+      </c>
+      <c r="DN4">
+        <v>110</v>
+      </c>
+      <c r="DO4" t="s">
+        <v>112</v>
+      </c>
+      <c r="DQ4">
+        <v>5</v>
+      </c>
+      <c r="DR4">
+        <v>2</v>
+      </c>
+      <c r="DS4" t="s">
+        <v>18</v>
+      </c>
+      <c r="DT4" t="s">
+        <v>5</v>
+      </c>
+      <c r="DU4">
+        <v>85</v>
+      </c>
+      <c r="DV4" t="s">
+        <v>499</v>
+      </c>
+      <c r="FQ4" s="1"/>
+      <c r="FR4" s="1"/>
+      <c r="FS4" s="1"/>
+      <c r="FT4" s="1"/>
+      <c r="FU4" s="1"/>
+      <c r="FV4" s="1"/>
+      <c r="FW4" s="1"/>
+      <c r="FX4" s="1"/>
+      <c r="FY4" s="1"/>
+    </row>
+    <row r="5" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="9"/>
+      <c r="FQ5" s="1"/>
+      <c r="FR5" s="1"/>
+      <c r="FS5" s="1"/>
+      <c r="FT5" s="1"/>
+      <c r="FU5" s="1"/>
+      <c r="FV5" s="1"/>
+      <c r="FW5" s="1"/>
+      <c r="FX5" s="1"/>
+      <c r="FY5" s="1"/>
+    </row>
+    <row r="6" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4"/>
+      <c r="FQ6" s="1"/>
+      <c r="FR6" s="1"/>
+      <c r="FS6" s="1"/>
+      <c r="FT6" s="1"/>
+      <c r="FU6" s="1"/>
+      <c r="FV6" s="1"/>
+      <c r="FW6" s="1"/>
+      <c r="FX6" s="1"/>
+      <c r="FY6" s="1"/>
+    </row>
+    <row r="7" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="4"/>
+      <c r="FQ7" s="1"/>
+      <c r="FR7" s="1"/>
+      <c r="FS7" s="1"/>
+      <c r="FT7" s="1"/>
+      <c r="FU7" s="1"/>
+      <c r="FV7" s="1"/>
+      <c r="FW7" s="1"/>
+      <c r="FX7" s="1"/>
+      <c r="FY7" s="1"/>
+    </row>
+    <row r="8" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="4"/>
+      <c r="G8" s="5"/>
+      <c r="FQ8" s="1"/>
+      <c r="FR8" s="1"/>
+      <c r="FS8" s="1"/>
+      <c r="FT8" s="1"/>
+      <c r="FU8" s="1"/>
+      <c r="FV8" s="1"/>
+      <c r="FW8" s="1"/>
+      <c r="FX8" s="1"/>
+      <c r="FY8" s="1"/>
+    </row>
+    <row r="9" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="4"/>
+      <c r="FQ9" s="1"/>
+      <c r="FR9" s="1"/>
+      <c r="FS9" s="1"/>
+      <c r="FT9" s="1"/>
+      <c r="FU9" s="1"/>
+      <c r="FV9" s="1"/>
+      <c r="FW9" s="1"/>
+      <c r="FX9" s="1"/>
+      <c r="FY9" s="1"/>
+    </row>
+    <row r="10" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4"/>
+      <c r="EP10" s="1"/>
+      <c r="EQ10" s="1"/>
+      <c r="FR10" s="1"/>
+      <c r="FS10" s="1"/>
+      <c r="FT10" s="1"/>
+      <c r="FU10" s="1"/>
+      <c r="FV10" s="1"/>
+      <c r="FW10" s="1"/>
+      <c r="FX10" s="1"/>
+      <c r="FY10" s="1"/>
+    </row>
+    <row r="11" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="4"/>
+      <c r="FQ11" s="1"/>
+      <c r="FR11" s="1"/>
+      <c r="FS11" s="1"/>
+      <c r="FT11" s="1"/>
+      <c r="FU11" s="1"/>
+      <c r="FV11" s="1"/>
+      <c r="FW11" s="1"/>
+      <c r="FX11" s="1"/>
+      <c r="FY11" s="1"/>
+    </row>
+    <row r="12" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="4"/>
+      <c r="FQ12" s="1"/>
+      <c r="FR12" s="1"/>
+      <c r="FS12" s="1"/>
+      <c r="FT12" s="1"/>
+      <c r="FU12" s="1"/>
+      <c r="FV12" s="1"/>
+      <c r="FW12" s="1"/>
+      <c r="FX12" s="1"/>
+      <c r="FY12" s="1"/>
+    </row>
+    <row r="13" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="4"/>
+      <c r="FQ13" s="1"/>
+      <c r="FR13" s="1"/>
+      <c r="FS13" s="1"/>
+      <c r="FT13" s="1"/>
+      <c r="FU13" s="1"/>
+      <c r="FV13" s="1"/>
+      <c r="FW13" s="1"/>
+      <c r="FX13" s="1"/>
+      <c r="FY13" s="1"/>
+    </row>
+    <row r="14" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4"/>
+      <c r="FQ14" s="1"/>
+      <c r="FR14" s="1"/>
+      <c r="FS14" s="1"/>
+      <c r="FT14" s="1"/>
+      <c r="FU14" s="1"/>
+      <c r="FV14" s="1"/>
+      <c r="FW14" s="1"/>
+      <c r="FX14" s="1"/>
+      <c r="FY14" s="1"/>
+    </row>
+    <row r="15" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="4"/>
+      <c r="FQ15" s="1"/>
+      <c r="FR15" s="1"/>
+      <c r="FS15" s="1"/>
+      <c r="FT15" s="1"/>
+      <c r="FU15" s="1"/>
+      <c r="FV15" s="1"/>
+      <c r="FW15" s="1"/>
+      <c r="FX15" s="1"/>
+      <c r="FY15" s="1"/>
+    </row>
+    <row r="16" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="4"/>
+      <c r="FQ16" s="1"/>
+      <c r="FR16" s="1"/>
+      <c r="FS16" s="1"/>
+      <c r="FT16" s="1"/>
+      <c r="FU16" s="1"/>
+      <c r="FV16" s="1"/>
+      <c r="FW16" s="1"/>
+      <c r="FX16" s="1"/>
+      <c r="FY16" s="1"/>
+    </row>
+    <row r="17" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="4"/>
+      <c r="FQ17" s="1"/>
+      <c r="FR17" s="1"/>
+      <c r="FS17" s="1"/>
+      <c r="FT17" s="1"/>
+      <c r="FU17" s="1"/>
+      <c r="FV17" s="1"/>
+      <c r="FW17" s="1"/>
+      <c r="FX17" s="1"/>
+      <c r="FY17" s="1"/>
+    </row>
+    <row r="18" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="4"/>
+      <c r="FQ18" s="1"/>
+      <c r="FR18" s="1"/>
+      <c r="FS18" s="1"/>
+      <c r="FT18" s="1"/>
+      <c r="FU18" s="1"/>
+      <c r="FV18" s="1"/>
+      <c r="FW18" s="1"/>
+      <c r="FX18" s="1"/>
+      <c r="FY18" s="1"/>
+    </row>
+    <row r="19" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="4"/>
+      <c r="EG19" s="1"/>
+      <c r="FQ19" s="1"/>
+      <c r="FR19" s="1"/>
+      <c r="FS19" s="1"/>
+      <c r="FT19" s="1"/>
+      <c r="FU19" s="1"/>
+      <c r="FV19" s="1"/>
+      <c r="FW19" s="1"/>
+      <c r="FX19" s="1"/>
+      <c r="FY19" s="1"/>
+    </row>
+    <row r="20" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="4"/>
+      <c r="FQ20" s="1"/>
+      <c r="FR20" s="1"/>
+      <c r="FS20" s="1"/>
+      <c r="FT20" s="1"/>
+      <c r="FU20" s="1"/>
+      <c r="FV20" s="1"/>
+      <c r="FW20" s="1"/>
+      <c r="FX20" s="1"/>
+      <c r="FY20" s="1"/>
+    </row>
+    <row r="21" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="4"/>
+      <c r="FQ21" s="1"/>
+      <c r="FR21" s="1"/>
+      <c r="FS21" s="1"/>
+      <c r="FT21" s="1"/>
+      <c r="FU21" s="1"/>
+      <c r="FV21" s="1"/>
+      <c r="FW21" s="1"/>
+      <c r="FX21" s="1"/>
+      <c r="FY21" s="1"/>
+    </row>
+    <row r="22" spans="1:181" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="4"/>
+      <c r="FQ22" s="1"/>
+      <c r="FR22" s="1"/>
+      <c r="FS22" s="1"/>
+      <c r="FT22" s="1"/>
+      <c r="FU22" s="1"/>
+      <c r="FV22" s="1"/>
+      <c r="FW22" s="1"/>
+      <c r="FX22" s="1"/>
+      <c r="FY22" s="1"/>
+    </row>
+    <row r="23" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ23" s="1"/>
+      <c r="FR23" s="1"/>
+      <c r="FS23" s="1"/>
+      <c r="FT23" s="1"/>
+      <c r="FU23" s="1"/>
+      <c r="FV23" s="1"/>
+      <c r="FW23" s="1"/>
+      <c r="FX23" s="1"/>
+      <c r="FY23" s="1"/>
+    </row>
+    <row r="24" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ24" s="1"/>
+      <c r="FR24" s="1"/>
+      <c r="FS24" s="1"/>
+      <c r="FT24" s="1"/>
+      <c r="FU24" s="1"/>
+      <c r="FV24" s="1"/>
+      <c r="FW24" s="1"/>
+      <c r="FX24" s="1"/>
+      <c r="FY24" s="1"/>
+    </row>
+    <row r="25" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ25" s="1"/>
+      <c r="FR25" s="1"/>
+      <c r="FS25" s="1"/>
+      <c r="FT25" s="1"/>
+      <c r="FU25" s="1"/>
+      <c r="FV25" s="1"/>
+      <c r="FW25" s="1"/>
+      <c r="FX25" s="1"/>
+      <c r="FY25" s="1"/>
+    </row>
+    <row r="26" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ26" s="1"/>
+      <c r="FR26" s="1"/>
+      <c r="FS26" s="1"/>
+      <c r="FT26" s="1"/>
+      <c r="FU26" s="1"/>
+      <c r="FV26" s="1"/>
+      <c r="FW26" s="1"/>
+      <c r="FX26" s="1"/>
+      <c r="FY26" s="1"/>
+    </row>
+    <row r="27" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ27" s="1"/>
+      <c r="FR27" s="1"/>
+      <c r="FS27" s="1"/>
+      <c r="FT27" s="1"/>
+      <c r="FU27" s="1"/>
+      <c r="FV27" s="1"/>
+      <c r="FW27" s="1"/>
+      <c r="FX27" s="1"/>
+      <c r="FY27" s="1"/>
+    </row>
+    <row r="28" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ28" s="1"/>
+      <c r="FR28" s="1"/>
+      <c r="FS28" s="1"/>
+      <c r="FT28" s="1"/>
+      <c r="FU28" s="1"/>
+      <c r="FV28" s="1"/>
+      <c r="FW28" s="1"/>
+      <c r="FX28" s="1"/>
+      <c r="FY28" s="1"/>
+    </row>
+    <row r="29" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ29" s="1"/>
+      <c r="FR29" s="1"/>
+      <c r="FS29" s="1"/>
+      <c r="FT29" s="1"/>
+      <c r="FU29" s="1"/>
+      <c r="FV29" s="1"/>
+      <c r="FW29" s="1"/>
+      <c r="FX29" s="1"/>
+      <c r="FY29" s="1"/>
+    </row>
+    <row r="30" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ30" s="1"/>
+      <c r="FR30" s="1"/>
+      <c r="FS30" s="1"/>
+      <c r="FT30" s="1"/>
+      <c r="FU30" s="1"/>
+      <c r="FV30" s="1"/>
+      <c r="FW30" s="1"/>
+      <c r="FX30" s="1"/>
+      <c r="FY30" s="1"/>
+    </row>
+    <row r="31" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ31" s="1"/>
+      <c r="FR31" s="1"/>
+      <c r="FS31" s="1"/>
+      <c r="FT31" s="1"/>
+      <c r="FU31" s="1"/>
+      <c r="FV31" s="1"/>
+      <c r="FW31" s="1"/>
+      <c r="FX31" s="1"/>
+      <c r="FY31" s="1"/>
+    </row>
+    <row r="32" spans="1:181" x14ac:dyDescent="0.2">
+      <c r="FQ32" s="1"/>
+      <c r="FR32" s="1"/>
+      <c r="FS32" s="1"/>
+      <c r="FT32" s="1"/>
+      <c r="FU32" s="1"/>
+      <c r="FV32" s="1"/>
+      <c r="FW32" s="1"/>
+      <c r="FX32" s="1"/>
+      <c r="FY32" s="1"/>
+    </row>
+    <row r="33" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ33" s="1"/>
+      <c r="FR33" s="1"/>
+      <c r="FS33" s="1"/>
+      <c r="FT33" s="1"/>
+      <c r="FU33" s="1"/>
+      <c r="FV33" s="1"/>
+      <c r="FW33" s="1"/>
+      <c r="FX33" s="1"/>
+      <c r="FY33" s="1"/>
+    </row>
+    <row r="34" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ34" s="1"/>
+      <c r="FR34" s="1"/>
+      <c r="FS34" s="1"/>
+      <c r="FT34" s="1"/>
+      <c r="FU34" s="1"/>
+      <c r="FV34" s="1"/>
+      <c r="FW34" s="1"/>
+      <c r="FX34" s="1"/>
+      <c r="FY34" s="1"/>
+    </row>
+    <row r="35" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ35" s="1"/>
+      <c r="FR35" s="1"/>
+      <c r="FS35" s="1"/>
+      <c r="FT35" s="1"/>
+      <c r="FU35" s="1"/>
+      <c r="FV35" s="1"/>
+      <c r="FW35" s="1"/>
+      <c r="FX35" s="1"/>
+      <c r="FY35" s="1"/>
+    </row>
+    <row r="36" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ36" s="1"/>
+      <c r="FR36" s="1"/>
+      <c r="FS36" s="1"/>
+      <c r="FT36" s="1"/>
+      <c r="FU36" s="1"/>
+      <c r="FV36" s="1"/>
+      <c r="FW36" s="1"/>
+      <c r="FX36" s="1"/>
+      <c r="FY36" s="1"/>
+    </row>
+    <row r="37" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ37" s="1"/>
+      <c r="FR37" s="1"/>
+      <c r="FS37" s="1"/>
+      <c r="FT37" s="1"/>
+      <c r="FU37" s="1"/>
+      <c r="FV37" s="1"/>
+      <c r="FW37" s="1"/>
+      <c r="FX37" s="1"/>
+      <c r="FY37" s="1"/>
+    </row>
+    <row r="38" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ38" s="1"/>
+      <c r="FR38" s="1"/>
+      <c r="FS38" s="1"/>
+      <c r="FT38" s="1"/>
+      <c r="FU38" s="1"/>
+      <c r="FV38" s="1"/>
+      <c r="FW38" s="1"/>
+      <c r="FX38" s="1"/>
+      <c r="FY38" s="1"/>
+    </row>
+    <row r="39" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ39" s="1"/>
+      <c r="FR39" s="1"/>
+      <c r="FS39" s="1"/>
+      <c r="FT39" s="1"/>
+      <c r="FU39" s="1"/>
+      <c r="FV39" s="1"/>
+      <c r="FW39" s="1"/>
+      <c r="FX39" s="1"/>
+      <c r="FY39" s="1"/>
+    </row>
+    <row r="40" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ40" s="1"/>
+      <c r="FR40" s="1"/>
+      <c r="FS40" s="1"/>
+      <c r="FT40" s="1"/>
+      <c r="FU40" s="1"/>
+      <c r="FV40" s="1"/>
+      <c r="FW40" s="1"/>
+      <c r="FX40" s="1"/>
+      <c r="FY40" s="1"/>
+    </row>
+    <row r="41" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ41" s="1"/>
+      <c r="FR41" s="1"/>
+      <c r="FS41" s="1"/>
+      <c r="FT41" s="1"/>
+      <c r="FU41" s="1"/>
+      <c r="FV41" s="1"/>
+      <c r="FW41" s="1"/>
+      <c r="FX41" s="1"/>
+      <c r="FY41" s="1"/>
+    </row>
+    <row r="42" spans="173:181" x14ac:dyDescent="0.2">
+      <c r="FQ42" s="1"/>
+      <c r="FR42" s="1"/>
+      <c r="FS42" s="1"/>
+      <c r="FT42" s="1"/>
+      <c r="FU42" s="1"/>
+      <c r="FV42" s="1"/>
+      <c r="FW42" s="1"/>
+      <c r="FX42" s="1"/>
+      <c r="FY42" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{955597E6-9568-7A4E-B8B0-5DB884128089}">
   <dimension ref="A1:GZ55"/>
